--- a/stories/arbres/ATOM-FAM.AID.001-03.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Solène veut mettre son manteau. La fermeture est difficile. C'est trop difficile. Solène va vers papa. Aller vers eux, c'est possible. Elle dit le besoin. Solène dit : papa, j'ai besoin d'aide. Papa l'écoute. Il tient le bas du manteau. Solène tire. Le manteau est fermé. Plus tard, dans le jardin, l'arrosoir est lourd. Solène se souvient. Elle va vers maman. Elle dit le besoin. Solène dit : maman, l'arrosoir est lourd. Maman tient l'anse avec elle. L'eau coule doucement. Même leçon, autre lieu. Quand c'est trop difficile, on va vers eux. On dit le besoin. Dire le besoin, c'est possible.</t>
+          <t>Solène veut mettre son manteau. La fermeture est difficile. C'est trop difficile. Solène va vers papa. Aller vers eux, c'est possible. Elle dit le besoin. Papa, j'ai besoin d'aide. Papa l'écoute. Il tient le bas du manteau. Solène tire. Le manteau est fermé. Plus tard, dans le jardin, l'arrosoir est lourd. Solène se souvient. Elle va vers maman. Elle dit le besoin. Maman, l'arrosoir est lourd. Maman tient l'anse avec elle. L'eau coule doucement. Même leçon, autre lieu. Quand c'est trop difficile, on va vers eux. On dit le besoin. Dire le besoin, c'est possible.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Solène veut mettre son manteau. La fermeture est difficile. C'est trop difficile. Solène va vers papa. Aller vers eux, c'est possible. Elle dit le besoin.
+enfant-f|Papa, j'ai besoin d'aide. Papa l'écoute. Il tient le bas du manteau.
+narrateur|Solène tire. Le manteau est fermé. Plus tard, dans le jardin, l'arrosoir est lourd. Solène se souvient. Elle va vers maman. Elle dit le besoin.
+enfant-f|Maman, l'arrosoir est lourd. Maman tient l'anse avec elle. L'eau coule doucement. Même leçon, autre lieu. Quand c'est trop difficile, on va vers eux. On dit le besoin. Dire le besoin, c'est possible.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1489,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|C'est trop difficile. Que fait Solène ?</t>
         </is>
       </c>
     </row>
@@ -1629,6 +1658,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Solène est allée vers papa. Puis vers maman. Elle a dit le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1787,6 +1821,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Les fleurs ont de l'eau. Solène range l'arrosoir.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1949,6 +1988,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1967,7 +2011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1984,6 +2028,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.AID.001-03.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 enfant-f|Maman, l'arrosoir est lourd. Maman tient l'anse avec elle. L'eau coule doucement. Même leçon, autre lieu. Quand c'est trop difficile, on va vers eux. On dit le besoin. Dire le besoin, c'est possible.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1502,7 @@
           <t>narrateur|C'est trop difficile. Que fait Solène ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1663,6 +1670,7 @@
           <t>narrateur|Solène est allée vers papa. Puis vers maman. Elle a dit le besoin.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1826,6 +1834,7 @@
           <t>narrateur|Les fleurs ont de l'eau. Solène range l'arrosoir.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1993,6 +2002,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2011,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2035,6 +2045,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2236,6 +2260,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.AID.001-03.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Solène va vers papa et maman</t>
+          <t>Les feuilles mouillées de Sarah</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Après la pluie, Sarah veut fermer son manteau, puis porter l'arrosoir. Trop difficile. Elle va vers papa, puis vers maman, et dit le besoin. Les fleurs boivent.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Solène veut mettre son manteau. La fermeture est difficile. C'est trop difficile. Solène va vers papa. Aller vers eux, c'est possible. Elle dit le besoin. Papa, j'ai besoin d'aide. Papa l'écoute. Il tient le bas du manteau. Solène tire. Le manteau est fermé. Plus tard, dans le jardin, l'arrosoir est lourd. Solène se souvient. Elle va vers maman. Elle dit le besoin. Maman, l'arrosoir est lourd. Maman tient l'anse avec elle. L'eau coule doucement. Même leçon, autre lieu. Quand c'est trop difficile, on va vers eux. On dit le besoin. Dire le besoin, c'est possible.</t>
+          <t>Les feuilles mouillées collent à la vitre de la porte. Elles sont vertes, avec un bord un peu brun. Une petite trace d'escargot brille sur le seuil. Le jardin sent la terre mouillée. Une goutte tombe encore de la gouttière. Elle fait tic, tout loin. Les bottes de Sarah sèchent près du tapis. Le tapis est rêche et gris. Il a plu toute la nuit, Sarah. Le jardin a soif, maintenant. En ce moment, Sarah prend son manteau bleu. Le tissu est un peu froid, un peu lourd. Je mets mon manteau, papa. Oui. On va voir les fleurs. Sarah enfile une manche. Puis l'autre manche. La fermeture est petite et lisse. Elle tire un peu. La fermeture reste en bas. C'est trop difficile. Elle ne monte pas. Sarah va vers papa. Aller vers eux, c'est possible. Elle dit le besoin. Papa, j'ai besoin d'aide. La fermeture est trop dure. Je t'écoute, Sarah. Je tiens le bas. Tu tires tout doucement. Papa tient le bas du manteau. Sarah tire. La fermeture monte. Ça fait zzz. Le manteau est fermé. Bravo. Tu as dit le besoin. Merci, papa. On ouvre la porte ? Oui, maman. Plus tard, dans le jardin, l'herbe est mouillée. Elle colle aux bottes. L'arrosoir vert est près des fleurs. Il est plein. Il est lourd. Sarah prend l'anse. L'anse est froide et lisse. L'arrosoir ne se lève pas bien. C'est trop difficile. Sarah se souvient. Elle va vers maman. Elle dit le besoin. Maman, l'arrosoir est lourd. J'ai besoin d'aide. Je t'écoute. On tient l'anse ensemble. Maman tient l'anse avec elle. L'eau coule doucement. Elle fait un filet brillant. Les fleurs boivent, toutes droites. Quand c'est trop difficile, on va vers eux. On dit le besoin. Dire le besoin, c'est possible. J'ai dit le besoin. Oui. Bravo, Sarah. Une feuille mouillée se décroche de la vitre. Elle tombe dans l'herbe, sans un bruit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,13 +1324,70 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Solène veut mettre son manteau. La fermeture est difficile. C'est trop difficile. Solène va vers papa. Aller vers eux, c'est possible. Elle dit le besoin.
-enfant-f|Papa, j'ai besoin d'aide. Papa l'écoute. Il tient le bas du manteau.
-narrateur|Solène tire. Le manteau est fermé. Plus tard, dans le jardin, l'arrosoir est lourd. Solène se souvient. Elle va vers maman. Elle dit le besoin.
-enfant-f|Maman, l'arrosoir est lourd. Maman tient l'anse avec elle. L'eau coule doucement. Même leçon, autre lieu. Quand c'est trop difficile, on va vers eux. On dit le besoin. Dire le besoin, c'est possible.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Les feuilles mouillées collent à la vitre de la porte.
+narrateur|Elles sont vertes, avec un bord un peu brun.
+narrateur|Une petite trace d'escargot brille sur le seuil.
+narrateur|Le jardin sent la terre mouillée.
+narrateur|Une goutte tombe encore de la gouttière.
+narrateur|Elle fait tic, tout loin.
+narrateur|Les bottes de Sarah sèchent près du tapis.
+narrateur|Le tapis est rêche et gris.
+papa|Il a plu toute la nuit, Sarah.
+maman|Le jardin a soif, maintenant.
+narrateur|En ce moment, Sarah prend son manteau bleu.
+narrateur|Le tissu est un peu froid, un peu lourd.
+enfant-f|Je mets mon manteau, papa.
+papa|Oui. On va voir les fleurs.
+narrateur|Sarah enfile une manche.
+narrateur|Puis l'autre manche.
+narrateur|La fermeture est petite et lisse.
+narrateur|Elle tire un peu.
+narrateur|La fermeture reste en bas.
+narrateur|C'est trop difficile.
+enfant-f|Elle ne monte pas.
+narrateur|Sarah va vers papa.
+narrateur|Aller vers eux, c'est possible.
+narrateur|Elle dit le besoin.
+enfant-f|Papa, j'ai besoin d'aide.
+enfant-f|La fermeture est trop dure.
+papa|Je t'écoute, Sarah.
+papa|Je tiens le bas. Tu tires tout doucement.
+narrateur|Papa tient le bas du manteau.
+narrateur|Sarah tire.
+narrateur|La fermeture monte. Ça fait zzz.
+narrateur|Le manteau est fermé.
+papa|Bravo. Tu as dit le besoin.
+enfant-f|Merci, papa.
+maman|On ouvre la porte ?
+enfant-f|Oui, maman.
+narrateur|Plus tard, dans le jardin, l'herbe est mouillée.
+narrateur|Elle colle aux bottes.
+narrateur|L'arrosoir vert est près des fleurs.
+narrateur|Il est plein. Il est lourd.
+narrateur|Sarah prend l'anse.
+narrateur|L'anse est froide et lisse.
+narrateur|L'arrosoir ne se lève pas bien.
+narrateur|C'est trop difficile.
+narrateur|Sarah se souvient.
+narrateur|Elle va vers maman.
+narrateur|Elle dit le besoin.
+enfant-f|Maman, l'arrosoir est lourd.
+enfant-f|J'ai besoin d'aide.
+maman|Je t'écoute.
+maman|On tient l'anse ensemble.
+narrateur|Maman tient l'anse avec elle.
+narrateur|L'eau coule doucement.
+narrateur|Elle fait un filet brillant.
+narrateur|Les fleurs boivent, toutes droites.
+maman|Quand c'est trop difficile, on va vers eux.
+papa|On dit le besoin.
+maman|Dire le besoin, c'est possible.
+enfant-f|J'ai dit le besoin.
+papa|Oui. Bravo, Sarah.
+narrateur|Une feuille mouillée se décroche de la vitre.
+narrateur|Elle tombe dans l'herbe, sans un bruit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1343,7 +1412,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>C'est trop difficile. Que fait Solène ?</t>
+          <t>C'est trop difficile. Que fait Sarah ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1499,10 +1568,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|C'est trop difficile. Que fait Solène ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|C'est trop difficile.
+narrateur|Que fait Sarah ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1527,7 +1596,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Solène est allée vers papa. Puis vers maman. Elle a dit le besoin.</t>
+          <t>Sarah est allée vers papa. Puis vers maman. Elle a dit le besoin. Tu es venue me le dire. Bravo. Tu as dit : l'arrosoir est lourd. C'est du bon travail, Sarah. Merci. Les fleurs ont un peu d'eau sur les pétales. Ça brille comme des perles.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1667,10 +1736,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Solène est allée vers papa. Puis vers maman. Elle a dit le besoin.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Sarah est allée vers papa.
+narrateur|Puis vers maman.
+narrateur|Elle a dit le besoin.
+papa|Tu es venue me le dire.
+papa|Bravo.
+maman|Tu as dit : l'arrosoir est lourd.
+maman|C'est du bon travail, Sarah.
+enfant-f|Merci.
+narrateur|Les fleurs ont un peu d'eau sur les pétales.
+narrateur|Ça brille comme des perles.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1695,7 +1772,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Les fleurs ont de l'eau. Solène range l'arrosoir.</t>
+          <t>Les fleurs ont de l'eau. Sarah range l'arrosoir près du mur. Tu as fini d'arroser ? Oui, maman. On rentre ? Tes mains sont froides. Un peu, papa. Papa ouvre la porte. L'entrée sent encore le tapis humide. On enlève les bottes ? Oui. Sarah pose les bottes près du tapis. Une goutte tombe encore, tout loin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1831,10 +1908,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Les fleurs ont de l'eau. Solène range l'arrosoir.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Les fleurs ont de l'eau.
+narrateur|Sarah range l'arrosoir près du mur.
+maman|Tu as fini d'arroser ?
+enfant-f|Oui, maman.
+papa|On rentre ? Tes mains sont froides.
+enfant-f|Un peu, papa.
+narrateur|Papa ouvre la porte.
+narrateur|L'entrée sent encore le tapis humide.
+maman|On enlève les bottes ?
+enfant-f|Oui.
+narrateur|Sarah pose les bottes près du tapis.
+narrateur|Une goutte tombe encore, tout loin.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1859,7 +1946,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit le besoin. Oui. Tu es venue vers nous. Bravo, Sarah. Tu as fait du bon travail. Les feuilles ne collent plus à la vitre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1999,10 +2086,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-f|J'ai dit le besoin.
+papa|Oui. Tu es venue vers nous.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+narrateur|Les feuilles ne collent plus à la vitre.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2021,7 +2112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2059,6 +2150,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.AID.001-03.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-03.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Solène veut mettre son manteau. La fermeture est difficile. C'est trop difficile. Solène va vers papa. &lt;emphasis level="moderate"&gt;aller&lt;/emphasis&gt; vers eux, c'est possible. Elle dit le besoin. Solène dit : papa, j'ai besoin d'aide. Papa l'écoute. Il tient le bas du manteau. Solène tire. Le manteau est fermé. Plus tard, dans le jardin, l'arrosoir est lourd. Solène se souvient. Elle va vers maman. Elle dit le besoin. Solène dit : maman, l'arrosoir est lourd. Maman tient l'anse avec elle. L'eau coule doucement. Même leçon, autre lieu. Quand c'est trop difficile, on va vers eux. On dit le besoin. Dire le besoin, c'est possible.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les feuilles mouillées collent à la vitre de la porte. Elles sont vertes, avec un bord un peu brun. Une petite trace d'escargot brille sur le seuil. Le jardin sent la terre mouillée. Une goutte tombe encore de la gouttière. Elle fait tic, tout loin. Les bottes de Sarah sèchent près du tapis. Le tapis est rêche et gris. Il a plu toute la nuit, Sarah. Le jardin a soif, maintenant. En ce moment, Sarah prend son manteau bleu. Le tissu est un peu froid, un peu lourd. Je mets mon manteau, papa. Oui. On va voir les fleurs. Sarah enfile une manche. Puis l'autre manche. La fermeture est petite et lisse. Elle tire un peu. La fermeture reste en bas. C'est trop difficile. Elle ne monte pas. Sarah va vers papa. Aller vers eux, c'est possible. Elle dit le besoin. Papa, j'ai besoin d'aide. La fermeture est trop dure. Je t'écoute, Sarah. Je tiens le bas. Tu tires tout doucement. Papa tient le bas du manteau. Sarah tire. La fermeture monte. Ça fait zzz. Le manteau est fermé. Bravo. Tu as dit le besoin. Merci, papa. On ouvre la porte ? Oui, maman. Plus tard, dans le jardin, l'herbe est mouillée. Elle colle aux bottes. L'arrosoir vert est près des fleurs. Il est plein. Il est lourd. Sarah prend l'anse. L'anse est froide et lisse. L'arrosoir ne se lève pas bien. C'est trop difficile. Sarah se souvient. Elle va vers maman. Elle dit le besoin. Maman, l'arrosoir est lourd. J'ai besoin d'aide. Je t'écoute. On tient l'anse ensemble. Maman tient l'anse avec elle. L'eau coule doucement. Elle fait un filet brillant. Les fleurs boivent, toutes droites. Quand c'est trop difficile, on va vers eux. On dit le besoin. Dire le besoin, c'est possible. J'ai dit le besoin. Oui. Bravo, Sarah. Une feuille mouillée se décroche de la vitre. Elle tombe dans l'herbe, sans un bruit.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;C'est trop difficile. Que fait Solène ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>C'est trop difficile. Que fait Sarah ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah est allée vers papa. Puis vers maman. Elle a dit le besoin. Tu es venue me le dire. Bravo. Tu as dit : l'arrosoir est lourd. C'est du bon travail, Sarah. Merci. Les fleurs ont un peu d'eau sur les pétales. Ça brille comme des perles.</t>
+          <t>Sarah est allée vers papa. Puis vers maman. Elle a dit le besoin. Tu es venue me le dire. Bravo. Tu as dit : l'arrosoir est lourd. Merci. Les fleurs ont un peu d'eau sur les pétales. Ça brille comme des perles.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Solène est allée vers papa. Puis vers maman. Elle a dit le besoin.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah est allée vers papa. Puis vers maman. Elle a dit le besoin. Tu es venue me le dire. Bravo. Tu as dit : l'arrosoir est lourd. Merci. Les fleurs ont un peu d'eau sur les pétales. Ça brille comme des perles.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1742,7 +1742,6 @@
 papa|Tu es venue me le dire.
 papa|Bravo.
 maman|Tu as dit : l'arrosoir est lourd.
-maman|C'est du bon travail, Sarah.
 enfant-f|Merci.
 narrateur|Les fleurs ont un peu d'eau sur les pétales.
 narrateur|Ça brille comme des perles.</t>
@@ -1777,7 +1776,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Les fleurs ont de l'eau. Solène range l'arrosoir.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les fleurs ont de l'eau. Sarah range l'arrosoir près du mur. Tu as fini d'arroser ? Oui, maman. On rentre ? Tes mains sont froides. Un peu, papa. Papa ouvre la porte. L'entrée sent encore le tapis humide. On enlève les bottes ? Oui. Sarah pose les bottes près du tapis. Une goutte tombe encore, tout loin.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1946,12 +1945,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit le besoin. Oui. Tu es venue vers nous. Bravo, Sarah. Tu as fait du bon travail. Les feuilles ne collent plus à la vitre. L'histoire est finie.</t>
+          <t>J'ai dit le besoin. Oui. Tu es venue vers nous. Bravo, Sarah. Les feuilles ne collent plus à la vitre.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit le besoin. Oui. Tu es venue vers nous. Bravo, Sarah. Les feuilles ne collent plus à la vitre.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2089,9 +2088,7 @@
           <t>enfant-f|J'ai dit le besoin.
 papa|Oui. Tu es venue vers nous.
 maman|Bravo, Sarah.
-maman|Tu as fait du bon travail.
-narrateur|Les feuilles ne collent plus à la vitre.
-narrateur|L'histoire est finie.</t>
+narrateur|Les feuilles ne collent plus à la vitre.</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2157,6 +2154,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.AID.001-03.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-03.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Solène, papa, maman</t>
+          <t>Sarah, papa, maman</t>
         </is>
       </c>
     </row>
